--- a/astro-site/public/dl/restaurant-schedule-templates/BONUS-01-shift-handover-log.xlsx
+++ b/astro-site/public/dl/restaurant-schedule-templates/BONUS-01-shift-handover-log.xlsx
@@ -1577,14 +1577,14 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="B47" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid tolerance" error="Type an amount between 0 and 100 (in your currency)." promptTitle="grupoA-v2 · Invalid tolerance" prompt="Below this amount, over or short, the cash count is treated as balanced. Five is typical at a shift change; raise or lower it to suit your restaurant." type="decimal" errorStyle="stop" operator="between">
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid tolerance" error="Type an amount between 0 and 100 (in your currency)." promptTitle="Cash count tolerance" prompt="Below this amount, over or short, the cash count is treated as balanced. Five is typical at a shift change; raise or lower it to suit your restaurant." type="decimal" errorStyle="stop" operator="between">
       <formula1>0</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation sqref="C17:C22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid severity" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="kitgp-v2 · Invalid severity" prompt="Without a list, each shift types a different word and the log stops being comparable from one day to the next." type="list" errorStyle="stop">
+    <dataValidation sqref="C17:C22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid severity" error="Pick a value from the list." promptTitle="Severity" prompt="Without a list, each shift types a different word and the log stops being comparable from one day to the next." type="list" errorStyle="stop">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="A25:A30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid priority" error="Pick a value from the list: the summary formulas look for this exact text." promptTitle="kitgp-v2 · Invalid priority" prompt="What the incoming shift looks at first." type="list" errorStyle="stop">
+    <dataValidation sqref="A25:A30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid priority" error="Pick a value from the list." promptTitle="Priority" prompt="What the incoming shift looks at first." type="list" errorStyle="stop">
       <formula1>"Urgent,High,Normal"</formula1>
     </dataValidation>
   </dataValidations>
